--- a/planilhas/LISTA DE PROCESSO DISPLAY ARAMADO G.xlsx
+++ b/planilhas/LISTA DE PROCESSO DISPLAY ARAMADO G.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\PROJETOS EM ANDAMENTO\PAINEL DE CONTROLE MTECH\PROGRAMAS\PROJETOS  - PAINEL PRODUÇÃO\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\PROJETOS EM ANDAMENTO\PAINEL DE CONTROLE MTECH\PROGRAMAS\PROJETOS - PAINEL PRODUÇÃO IA\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19B96C2-72D5-4222-B092-90A4055B0C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE11555-9E02-41B0-B381-6BCEA103DF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="65">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>0,75 Nest 17</t>
-  </si>
-  <si>
-    <t>0,75 Nest 18</t>
   </si>
   <si>
     <t>2,65mm Nest 1</t>
@@ -241,7 +238,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -274,7 +271,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -621,7 +618,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E29" si="0">F3/1198</f>
+        <f t="shared" ref="E3:E28" si="0">F3/1198</f>
         <v>0.4991652754590985</v>
       </c>
       <c r="F3">
@@ -769,10 +766,10 @@
       </c>
       <c r="E10" s="1">
         <f t="shared" si="0"/>
-        <v>6.3439065108514187E-2</v>
+        <v>6.0934891485809682E-2</v>
       </c>
       <c r="F10">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -790,10 +787,10 @@
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>9.098497495826377E-2</v>
+        <v>4.1736227045075125E-2</v>
       </c>
       <c r="F11">
-        <v>109</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -811,10 +808,10 @@
       </c>
       <c r="E12" s="1">
         <f t="shared" si="0"/>
-        <v>6.7612687813021696E-2</v>
+        <v>9.9332220367278803E-2</v>
       </c>
       <c r="F12">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -832,10 +829,10 @@
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>3.4223706176961605E-2</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F13">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -853,10 +850,10 @@
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+        <v>9.2654424040066782E-2</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -874,10 +871,10 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+        <v>2.5041736227045075E-3</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -895,10 +892,10 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+        <v>6.6777963272120202E-3</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -916,10 +913,10 @@
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>4.006677796327212E-2</v>
+        <v>3.6727879799666109E-2</v>
       </c>
       <c r="F17">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -937,10 +934,10 @@
       </c>
       <c r="E18" s="1">
         <f t="shared" si="0"/>
-        <v>2.4207011686143573E-2</v>
+        <v>1.4190317195325543E-2</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -958,10 +955,10 @@
       </c>
       <c r="E19" s="1">
         <f t="shared" si="0"/>
-        <v>4.757929883138564E-2</v>
+        <v>0.1310517529215359</v>
       </c>
       <c r="F19">
-        <v>57</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -979,10 +976,10 @@
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
-        <v>2.0868113522537562E-2</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F20">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1000,10 +997,10 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
-        <v>1.0851419031719533E-2</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F21">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1021,10 +1018,10 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
-        <v>2.337228714524207E-2</v>
+        <v>2.5041736227045075E-3</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1042,10 +1039,10 @@
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
-        <v>2.0868113522537562E-2</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F23">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1063,10 +1060,10 @@
       </c>
       <c r="E24" s="1">
         <f t="shared" si="0"/>
-        <v>4.340567612687813E-2</v>
+        <v>8.3472454090150246E-3</v>
       </c>
       <c r="F24">
-        <v>52</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1084,10 +1081,10 @@
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+        <v>1.4190317195325543E-2</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1105,10 +1102,10 @@
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
-        <v>2.4207011686143573E-2</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F26">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1126,10 +1123,10 @@
       </c>
       <c r="E27" s="1">
         <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+        <v>5.008347245409015E-3</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1147,10 +1144,10 @@
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
-        <v>5.008347245409015E-3</v>
+        <v>8.3472454090150253E-4</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1161,17 +1158,16 @@
         <v>20</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="1">
-        <f t="shared" si="0"/>
-        <v>8.3472454090150253E-4</v>
+      <c r="E29">
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1202,16 +1198,16 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2396</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1228,10 +1224,10 @@
         <v>47</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32">
-        <v>1198</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,16 +1238,16 @@
         <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
         <v>48</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>2396</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1262,16 +1258,16 @@
         <v>20</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>9584</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1282,16 +1278,16 @@
         <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F35">
-        <v>1198</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1305,7 +1301,7 @@
         <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="E36">
         <v>4</v>
@@ -1348,10 +1344,10 @@
         <v>51</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>4792</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1368,10 +1364,10 @@
         <v>52</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>2396</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1388,10 +1384,10 @@
         <v>53</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>1198</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1442,16 +1438,16 @@
         <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
         <v>56</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>2396</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1525,13 +1521,13 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>1198</v>
+        <v>4792</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1545,13 +1541,13 @@
         <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>4792</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1585,7 +1581,7 @@
         <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -1605,7 +1601,7 @@
         <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -1651,26 +1647,6 @@
         <v>1</v>
       </c>
       <c r="F53">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54">
-        <v>1</v>
-      </c>
-      <c r="F54">
         <v>1198</v>
       </c>
     </row>

--- a/planilhas/LISTA DE PROCESSO DISPLAY ARAMADO G.xlsx
+++ b/planilhas/LISTA DE PROCESSO DISPLAY ARAMADO G.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\PROJETOS EM ANDAMENTO\PAINEL DE CONTROLE MTECH\PROGRAMAS\PROJETOS - PAINEL PRODUÇÃO IA\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE11555-9E02-41B0-B381-6BCEA103DF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0289A0-E155-41E2-BFEF-016AB3DF8ED9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="81">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -231,6 +231,54 @@
   </si>
   <si>
     <t>Apoio Rodizio</t>
+  </si>
+  <si>
+    <t>0,75 Nest 1 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 2 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 3 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 4 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 5 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 6 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 7 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 8 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 9 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 10 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 11 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 12 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 13 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 14 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 15 AJUSTADA</t>
+  </si>
+  <si>
+    <t>0,75 Nest 16 AJUSTADA</t>
   </si>
 </sst>
 </file>
@@ -552,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
@@ -1650,6 +1698,326 @@
         <v>1198</v>
       </c>
     </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>19</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>65</v>
+      </c>
+      <c r="E54">
+        <v>3.6727879999999997E-2</v>
+      </c>
+      <c r="F54">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E55">
+        <v>8.3472500000000003E-4</v>
+      </c>
+      <c r="F55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56">
+        <v>8.4307178999999996E-2</v>
+      </c>
+      <c r="F56">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>19</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57">
+        <v>2.3372286999999999E-2</v>
+      </c>
+      <c r="F57">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58">
+        <v>0.105175292</v>
+      </c>
+      <c r="F58">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>19</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>70</v>
+      </c>
+      <c r="E59">
+        <v>1.6694489999999999E-3</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60">
+        <v>7.5125210000000003E-3</v>
+      </c>
+      <c r="F60">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>19</v>
+      </c>
+      <c r="B61" t="s">
+        <v>20</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>72</v>
+      </c>
+      <c r="E61">
+        <v>8.3472500000000003E-4</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>19</v>
+      </c>
+      <c r="B62" t="s">
+        <v>20</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>73</v>
+      </c>
+      <c r="E62">
+        <v>8.3472500000000003E-4</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>74</v>
+      </c>
+      <c r="E63">
+        <v>1.6694489999999999E-3</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>75</v>
+      </c>
+      <c r="E64">
+        <v>1.0016694E-2</v>
+      </c>
+      <c r="F64">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65">
+        <v>1.6694489999999999E-3</v>
+      </c>
+      <c r="F65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66">
+        <v>5.0083469999999998E-3</v>
+      </c>
+      <c r="F66">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67">
+        <v>2.1702837999999999E-2</v>
+      </c>
+      <c r="F67">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68">
+        <v>3.0050082999999998E-2</v>
+      </c>
+      <c r="F68">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>20</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>80</v>
+      </c>
+      <c r="E69">
+        <v>8.3472500000000003E-4</v>
+      </c>
+      <c r="F69">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
